--- a/output/tetris-gr.xlsx
+++ b/output/tetris-gr.xlsx
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>2314</v>
+        <v>2274</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">

--- a/output/tetris-gr.xlsx
+++ b/output/tetris-gr.xlsx
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>2274</v>
+        <v>2306</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">

--- a/output/tetris-gr.xlsx
+++ b/output/tetris-gr.xlsx
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>2306</v>
+        <v>2316</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">

--- a/output/tetris-gr.xlsx
+++ b/output/tetris-gr.xlsx
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>2316</v>
+        <v>2580</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">

--- a/output/tetris-gr.xlsx
+++ b/output/tetris-gr.xlsx
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>2580</v>
+        <v>2590</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">

--- a/output/tetris-gr.xlsx
+++ b/output/tetris-gr.xlsx
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>2590</v>
+        <v>2580</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">

--- a/output/tetris-gr.xlsx
+++ b/output/tetris-gr.xlsx
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>2580</v>
+        <v>2586</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">

--- a/output/tetris-gr.xlsx
+++ b/output/tetris-gr.xlsx
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>2586</v>
+        <v>2580</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">

--- a/output/tetris-gr.xlsx
+++ b/output/tetris-gr.xlsx
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>2580</v>
+        <v>2720</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">

--- a/output/tetris-gr.xlsx
+++ b/output/tetris-gr.xlsx
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>2720</v>
+        <v>2580</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">

--- a/output/tetris-gr.xlsx
+++ b/output/tetris-gr.xlsx
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>2580</v>
+        <v>2548</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">

--- a/output/tetris-gr.xlsx
+++ b/output/tetris-gr.xlsx
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>2548</v>
+        <v>2556</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">

--- a/output/tetris-gr.xlsx
+++ b/output/tetris-gr.xlsx
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>2556</v>
+        <v>2732</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">

--- a/output/tetris-gr.xlsx
+++ b/output/tetris-gr.xlsx
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>2732</v>
+        <v>2580</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">

--- a/output/tetris-gr.xlsx
+++ b/output/tetris-gr.xlsx
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>2580</v>
+        <v>2882</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">

--- a/output/tetris-gr.xlsx
+++ b/output/tetris-gr.xlsx
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>2882</v>
+        <v>2580</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">

--- a/output/tetris-gr.xlsx
+++ b/output/tetris-gr.xlsx
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>2580</v>
+        <v>2756</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">

--- a/output/tetris-gr.xlsx
+++ b/output/tetris-gr.xlsx
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>2756</v>
+        <v>2808</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">

--- a/output/tetris-gr.xlsx
+++ b/output/tetris-gr.xlsx
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>2808</v>
+        <v>2670</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">

--- a/output/tetris-gr.xlsx
+++ b/output/tetris-gr.xlsx
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>2670</v>
+        <v>2580</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">

--- a/output/tetris-gr.xlsx
+++ b/output/tetris-gr.xlsx
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>2580</v>
+        <v>2676</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">

--- a/output/tetris-gr.xlsx
+++ b/output/tetris-gr.xlsx
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>2676</v>
+        <v>2578</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">

--- a/output/tetris-gr.xlsx
+++ b/output/tetris-gr.xlsx
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>2578</v>
+        <v>2652</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">

--- a/output/tetris-gr.xlsx
+++ b/output/tetris-gr.xlsx
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>2652</v>
+        <v>2664</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">

--- a/output/tetris-gr.xlsx
+++ b/output/tetris-gr.xlsx
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>2664</v>
+        <v>2502</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">

--- a/output/tetris-gr.xlsx
+++ b/output/tetris-gr.xlsx
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>2502</v>
+        <v>2508</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">

--- a/output/tetris-gr.xlsx
+++ b/output/tetris-gr.xlsx
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>2508</v>
+        <v>2474</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">

--- a/output/tetris-gr.xlsx
+++ b/output/tetris-gr.xlsx
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>2474</v>
+        <v>2510</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">

--- a/output/tetris-gr.xlsx
+++ b/output/tetris-gr.xlsx
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>2510</v>
+        <v>2460</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">

--- a/output/tetris-gr.xlsx
+++ b/output/tetris-gr.xlsx
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>2460</v>
+        <v>2508</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">

--- a/output/tetris-gr.xlsx
+++ b/output/tetris-gr.xlsx
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>2508</v>
+        <v>2528</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">

--- a/output/tetris-gr.xlsx
+++ b/output/tetris-gr.xlsx
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>2528</v>
+        <v>2472</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">

--- a/output/tetris-gr.xlsx
+++ b/output/tetris-gr.xlsx
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>2472</v>
+        <v>2510</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">

--- a/output/tetris-gr.xlsx
+++ b/output/tetris-gr.xlsx
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>2510</v>
+        <v>2512</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">

--- a/output/tetris-gr.xlsx
+++ b/output/tetris-gr.xlsx
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>2512</v>
+        <v>2508</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">

--- a/output/tetris-gr.xlsx
+++ b/output/tetris-gr.xlsx
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>2508</v>
+        <v>2550</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">

--- a/output/tetris-gr.xlsx
+++ b/output/tetris-gr.xlsx
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>2550</v>
+        <v>2602</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">

--- a/output/tetris-gr.xlsx
+++ b/output/tetris-gr.xlsx
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>2602</v>
+        <v>2544</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">

--- a/output/tetris-gr.xlsx
+++ b/output/tetris-gr.xlsx
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>2544</v>
+        <v>2614</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">

--- a/output/tetris-gr.xlsx
+++ b/output/tetris-gr.xlsx
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>2614</v>
+        <v>2580</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">

--- a/output/tetris-gr.xlsx
+++ b/output/tetris-gr.xlsx
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>2580</v>
+        <v>2602</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">

--- a/output/tetris-gr.xlsx
+++ b/output/tetris-gr.xlsx
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>2602</v>
+        <v>2538</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
@@ -691,7 +691,7 @@
         </is>
       </c>
       <c r="D11" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1">

--- a/output/tetris-gr.xlsx
+++ b/output/tetris-gr.xlsx
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>2538</v>
+        <v>2580</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">

--- a/output/tetris-gr.xlsx
+++ b/output/tetris-gr.xlsx
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>2580</v>
+        <v>1916</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">

--- a/output/tetris-gr.xlsx
+++ b/output/tetris-gr.xlsx
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>1916</v>
+        <v>1720</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">

--- a/output/tetris-gr.xlsx
+++ b/output/tetris-gr.xlsx
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>1720</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">

--- a/output/tetris-gr.xlsx
+++ b/output/tetris-gr.xlsx
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>1176</v>
+        <v>862</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">

--- a/output/tetris-gr.xlsx
+++ b/output/tetris-gr.xlsx
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>862</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">

--- a/output/tetris-gr.xlsx
+++ b/output/tetris-gr.xlsx
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>0</v>
+        <v>322</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">

--- a/output/tetris-gr.xlsx
+++ b/output/tetris-gr.xlsx
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>322</v>
+        <v>824</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">

--- a/output/tetris-gr.xlsx
+++ b/output/tetris-gr.xlsx
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>824</v>
+        <v>1684</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">

--- a/output/tetris-gr.xlsx
+++ b/output/tetris-gr.xlsx
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>1684</v>
+        <v>1932</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">

--- a/output/tetris-gr.xlsx
+++ b/output/tetris-gr.xlsx
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>1932</v>
+        <v>2580</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">

--- a/output/tetris-gr.xlsx
+++ b/output/tetris-gr.xlsx
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>2580</v>
+        <v>2628</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">

--- a/output/tetris-gr.xlsx
+++ b/output/tetris-gr.xlsx
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>2628</v>
+        <v>2580</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">

--- a/output/tetris-gr.xlsx
+++ b/output/tetris-gr.xlsx
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>2580</v>
+        <v>2616</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">

--- a/output/tetris-gr.xlsx
+++ b/output/tetris-gr.xlsx
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>2616</v>
+        <v>2580</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">

--- a/output/tetris-gr.xlsx
+++ b/output/tetris-gr.xlsx
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>2580</v>
+        <v>2584</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">

--- a/output/tetris-gr.xlsx
+++ b/output/tetris-gr.xlsx
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>2584</v>
+        <v>2580</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">

--- a/output/tetris-gr.xlsx
+++ b/output/tetris-gr.xlsx
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>2580</v>
+        <v>2544</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">

--- a/output/tetris-gr.xlsx
+++ b/output/tetris-gr.xlsx
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>2544</v>
+        <v>2506</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">

--- a/output/tetris-gr.xlsx
+++ b/output/tetris-gr.xlsx
@@ -603,7 +603,7 @@
         </is>
       </c>
       <c r="D6" s="6" t="n">
-        <v>2506</v>
+        <v>2430</v>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1">
@@ -659,7 +659,7 @@
         </is>
       </c>
       <c r="D9" s="6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
